--- a/sheets/민요/검수/강원도 아리랑.xlsx
+++ b/sheets/민요/검수/강원도 아리랑.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,63 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2264,8 +2401,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -2276,533 +2417,480 @@
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">강원도 아리랑 — 민요채보-3/강원도 아리랑.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">강원도 아리랑</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">어리</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">아리</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">아라</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="C4" s="20"/>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아리</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I4" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아라</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C5" s="21"/>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E5" s="21"/>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G5" s="21"/>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I5" s="21"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E6" s="19"/>
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="G6" s="19"/>
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">古</t>
         </is>
       </c>
-      <c r="I6" s="5"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="I6" s="22"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="20"/>
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 仲</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="I7" s="20"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E8" s="21"/>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G8" s="21"/>
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="I8" s="21"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G9" s="23"/>
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="I9" s="19"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="20"/>
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="20"/>
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="20"/>
+      <c r="H10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="I10" s="20"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 仲</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">단</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 仲</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">넘</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">古</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E13" s="20"/>
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="G13" s="20"/>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 ‹</t>
         </is>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="25"/>
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="21"/>
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 ‹</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:I2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="100"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/강원도 아리랑.xlsx
+++ b/sheets/민요/검수/강원도 아리랑.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="138">
   <si>
     <t xml:space="preserve">강원도 아리랑</t>
   </si>
@@ -395,6 +395,10 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">살구
+나무</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="22"/>
@@ -432,15 +436,12 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">–
-–汰</t>
-  </si>
-  <si>
-    <t xml:space="preserve">–</t>
-  </si>
-  <si>
-    <t xml:space="preserve">–
-–南</t>
+    <t xml:space="preserve">아주
+까리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아리
+아리</t>
   </si>
   <si>
     <r>
@@ -448,6 +449,53 @@
         <sz val="22"/>
         <rFont val="맑은 고딕"/>
         <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">–
+–</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="24"/>
+        <rFont val="궁서체"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">汰</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">–</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="22"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">–
+–</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="22"/>
+        <rFont val="궁서체"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">汰</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">–
+–南</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="24"/>
+        <rFont val="궁서체"/>
+        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㴌
@@ -463,6 +511,10 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">정
+자</t>
+  </si>
+  <si>
     <t xml:space="preserve">㳞</t>
   </si>
   <si>
@@ -471,6 +523,10 @@
   <si>
     <t xml:space="preserve">無 無
 無無</t>
+  </si>
+  <si>
+    <t xml:space="preserve">쓰리
+쓰리</t>
   </si>
   <si>
     <r>
@@ -501,12 +557,47 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">로
+마</t>
+  </si>
+  <si>
     <t xml:space="preserve">㳞
 㴌汰</t>
   </si>
   <si>
-    <t xml:space="preserve">㳞㴌
+    <t xml:space="preserve">자
+는</t>
+  </si>
+  <si>
+    <t xml:space="preserve">개
+로</t>
+  </si>
+  <si>
+    <t xml:space="preserve">나
+보</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="22"/>
+        <rFont val="궁서체"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">㳞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="22"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">㴌
 –</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">구</t>
   </si>
   <si>
     <r>
@@ -537,8 +628,32 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">㴌汰
-無南</t>
+    <r>
+      <rPr>
+        <sz val="22"/>
+        <rFont val="궁서체"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">㴌汰
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="22"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">無南</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">경
+자</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어
+간</t>
   </si>
   <si>
     <r>
@@ -553,12 +668,22 @@
     <r>
       <rPr>
         <sz val="22"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
+        <rFont val="궁서체"/>
+        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">無南</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">라
+리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">요</t>
   </si>
   <si>
     <t xml:space="preserve">–
@@ -572,7 +697,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -602,10 +727,22 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="궁서체"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
-      <sz val="14"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="궁서체"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -618,6 +755,18 @@
       <sz val="22"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -640,7 +789,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -652,6 +801,20 @@
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
@@ -681,7 +844,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -706,23 +869,75 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2666,262 +2881,280 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:O10"/>
-  <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B2:O10"/>
+  <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="6" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="6" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="6" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="6" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="6" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="6" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="6" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="6" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="6" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="6" width="6"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16" style="6" width="8.5"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="7" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="8" t="s">
+      <c r="I3" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="J3" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="M3" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="8"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="I4" s="16"/>
+      <c r="J4" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="K4" s="18"/>
+      <c r="L4" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="M4" s="18"/>
+      <c r="N4" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="O4" s="18"/>
+    </row>
+    <row r="5" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="8"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="M5" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="O5" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="8"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="M6" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="N6" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="O6" s="18"/>
+    </row>
+    <row r="7" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="8"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="O7" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="L3" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="M5" s="4"/>
-      <c r="N5" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="O5" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="M6" s="5"/>
-      <c r="N6" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="O6" s="4"/>
-    </row>
-    <row r="7" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="8" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="8"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="M8" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="N8" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="O8" s="22" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="8"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="8" t="s">
+      <c r="I9" s="11"/>
+      <c r="J9" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="M7" s="5"/>
-      <c r="N7" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="K8" s="5" t="s">
+      <c r="M9" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="L8" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="M8" s="4"/>
-      <c r="N8" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="O8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="9" t="s">
+      <c r="N9" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="M9" s="4"/>
-      <c r="N9" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>58</v>
+      <c r="O9" s="13" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="M10" s="4"/>
-      <c r="N10" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="O10" s="4"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="I10" s="16"/>
+      <c r="J10" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="K10" s="18"/>
+      <c r="L10" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="M10" s="18"/>
+      <c r="N10" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="O10" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/강원도 아리랑.xlsx
+++ b/sheets/민요/검수/강원도 아리랑.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">기호</t>
   </si>
   <si>
-    <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+    <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
   </si>
   <si>
     <t xml:space="preserve">노란 칸</t>
@@ -181,7 +181,7 @@
     <t xml:space="preserve">첫 仲 왼쪽에 삼수변? 불확실</t>
   </si>
   <si>
-    <t xml:space="preserve">―</t>
+    <t xml:space="preserve">–</t>
   </si>
   <si>
     <t xml:space="preserve">姑</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">아리</t>
   </si>
   <si>
-    <t xml:space="preserve">―|太</t>
-  </si>
-  <si>
-    <t xml:space="preserve">―
+    <t xml:space="preserve">–|太</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–
 太</t>
   </si>
   <si>
@@ -360,8 +360,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -369,8 +368,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無
@@ -378,8 +376,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -387,8 +384,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -401,8 +397,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -410,8 +405,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">仲
@@ -419,8 +413,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -428,8 +421,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">仲</t>
@@ -446,8 +438,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">–
@@ -455,7 +446,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -469,8 +459,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">–
@@ -478,7 +467,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -493,7 +481,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -503,8 +490,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌</t>
@@ -531,8 +517,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰
@@ -540,8 +525,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -549,8 +533,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">仲</t>
@@ -579,7 +562,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -588,8 +570,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌
@@ -602,8 +583,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無汰
@@ -611,8 +591,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -620,8 +599,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -630,7 +608,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -640,8 +617,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無南</t>
@@ -658,8 +634,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="22"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰
@@ -667,7 +642,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -697,32 +671,32 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -747,13 +721,13 @@
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
@@ -767,6 +741,17 @@
       <name val="궁서체"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -844,7 +829,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -938,6 +923,62 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2885,276 +2926,276 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="6" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="6" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="6" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="6" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="6" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="6" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="6" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="6" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="6" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="6" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="24" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="25" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="24" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="25" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="24" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="25" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="24" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="25" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="24" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="25" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="24" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="25" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="24" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="25" width="6"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16" style="6" width="8.5"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
     </row>
     <row r="3" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="8"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="10" t="s">
+      <c r="B3" s="27"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="M3" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="N3" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="O3" s="30" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="8"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="15" t="s">
+      <c r="B4" s="27"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="I4" s="16"/>
-      <c r="J4" s="17" t="s">
+      <c r="I4" s="34"/>
+      <c r="J4" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="K4" s="18"/>
-      <c r="L4" s="15" t="s">
+      <c r="K4" s="34"/>
+      <c r="L4" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="M4" s="18"/>
-      <c r="N4" s="15" t="s">
+      <c r="M4" s="34"/>
+      <c r="N4" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="O4" s="18"/>
+      <c r="O4" s="34"/>
     </row>
     <row r="5" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="19" t="s">
+      <c r="B5" s="27"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="35" t="s">
         <v>115</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="L5" s="17" t="s">
+      <c r="L5" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="M5" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="N5" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="O5" s="13" t="s">
+      <c r="O5" s="30" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="8"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="20" t="s">
+      <c r="B6" s="27"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="J6" s="17" t="s">
+      <c r="J6" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="K6" s="22" t="s">
+      <c r="K6" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="L6" s="20" t="s">
+      <c r="L6" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="M6" s="22" t="s">
+      <c r="M6" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="N6" s="15" t="s">
+      <c r="N6" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="O6" s="18"/>
+      <c r="O6" s="34"/>
     </row>
     <row r="7" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="19" t="s">
+      <c r="B7" s="27"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="L7" s="17" t="s">
+      <c r="L7" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="M7" s="13" t="s">
+      <c r="M7" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="N7" s="17" t="s">
+      <c r="N7" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="O7" s="13" t="s">
+      <c r="O7" s="30" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="20" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="J8" s="17" t="s">
+      <c r="J8" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="K8" s="22" t="s">
+      <c r="K8" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="L8" s="20" t="s">
+      <c r="L8" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="M8" s="22" t="s">
+      <c r="M8" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="N8" s="20" t="s">
+      <c r="N8" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="O8" s="22" t="s">
+      <c r="O8" s="37" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="8"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="23" t="s">
+      <c r="B9" s="27"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="8" t="s">
+      <c r="I9" s="30"/>
+      <c r="J9" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="K9" s="13" t="s">
+      <c r="K9" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="L9" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="M9" s="13" t="s">
+      <c r="M9" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="N9" s="8" t="s">
+      <c r="N9" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="O9" s="13" t="s">
+      <c r="O9" s="30" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="15" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="I10" s="16"/>
-      <c r="J10" s="15" t="s">
+      <c r="I10" s="34"/>
+      <c r="J10" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="K10" s="18"/>
-      <c r="L10" s="15" t="s">
+      <c r="K10" s="34"/>
+      <c r="L10" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="M10" s="18"/>
-      <c r="N10" s="15" t="s">
+      <c r="M10" s="34"/>
+      <c r="N10" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="O10" s="18"/>
+      <c r="O10" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
